--- a/data/trans_dic/P64D1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P64D1_R-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,83; 24,49</t>
+          <t>13,97; 26,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,24; 34,27</t>
+          <t>21,78; 33,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,92; 26,34</t>
+          <t>18,67; 27,51</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,35; 28,33</t>
+          <t>15,06; 28,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,75; 36,25</t>
+          <t>26,47; 38,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,52; 29,44</t>
+          <t>21,68; 31,15</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,16; 34,52</t>
+          <t>19,72; 33,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,25; 51,12</t>
+          <t>36,3; 51,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,53; 39,64</t>
+          <t>29,15; 39,38</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,69; 32,14</t>
+          <t>18,84; 35,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,43; 81,02</t>
+          <t>28,29; 42,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,84; 63,92</t>
+          <t>25,12; 36,18</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,39%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,59; 52,39</t>
+          <t>36,95; 51,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51,22; 63,98</t>
+          <t>50,78; 64,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,95; 56,31</t>
+          <t>45,36; 55,75</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,47%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,27; 37,66</t>
+          <t>22,91; 37,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,55; 62,51</t>
+          <t>45,96; 63,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,77; 44,84</t>
+          <t>34,07; 45,36</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,04; 15,57</t>
+          <t>8,19; 15,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,3; 28,87</t>
+          <t>21,79; 29,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,76; 20,66</t>
+          <t>15,62; 21,45</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,62; 32,19</t>
+          <t>26,88; 36,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>41,83; 52,76</t>
+          <t>41,45; 51,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,1; 38,96</t>
+          <t>34,13; 41,3</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13,95; 24,34</t>
+          <t>22,56; 26,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35,38; 48,59</t>
+          <t>35,56; 39,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23,6; 33,33</t>
+          <t>28,84; 31,94</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33260</t>
+          <t>38832</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39295</t>
+          <t>41370</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72555</t>
+          <t>80202</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22730; 47062</t>
+          <t>28006; 53299</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30656; 49463</t>
+          <t>33268; 50588</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56922; 88628</t>
+          <t>65947; 97183</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>50145</t>
+          <t>55714</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>49745</t>
+          <t>55514</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99890</t>
+          <t>111228</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35234; 69573</t>
+          <t>38329; 72873</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39342; 60047</t>
+          <t>45947; 67167</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80286; 121067</t>
+          <t>92840; 133384</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39309</t>
+          <t>38783</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51720</t>
+          <t>53980</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91029</t>
+          <t>92763</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29980; 51324</t>
+          <t>29507; 49489</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>42598; 61780</t>
+          <t>44660; 63701</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76898; 106860</t>
+          <t>79484; 107378</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>38430</t>
+          <t>55400</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>124223</t>
+          <t>62881</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>162653</t>
+          <t>118282</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27939; 53806</t>
+          <t>39537; 75167</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65815; 209656</t>
+          <t>51248; 76984</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>101620; 272424</t>
+          <t>98213; 141464</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>50903</t>
+          <t>59482</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>62036</t>
+          <t>69313</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112939</t>
+          <t>128795</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>41800; 59854</t>
+          <t>50308; 70520</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>54866; 68535</t>
+          <t>60654; 77065</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>101720; 124638</t>
+          <t>115945; 142490</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>40305</t>
+          <t>40645</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>46510</t>
+          <t>47542</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>86815</t>
+          <t>88186</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>30078; 50868</t>
+          <t>31172; 51095</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>38490; 54008</t>
+          <t>40150; 55315</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>74787; 99315</t>
+          <t>76121; 101359</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>37695</t>
+          <t>45936</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>74220</t>
+          <t>93290</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>111915</t>
+          <t>139226</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>26867; 52032</t>
+          <t>31741; 61594</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>62264; 88556</t>
+          <t>78835; 107727</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>94628; 132411</t>
+          <t>117013; 160716</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>117938</t>
+          <t>142286</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>128507</t>
+          <t>146676</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>246445</t>
+          <t>288962</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>41574; 202248</t>
+          <t>122298; 165563</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>113394; 143031</t>
+          <t>129405; 160657</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>117820; 350445</t>
+          <t>261805; 316830</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>407985</t>
+          <t>477078</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>576256</t>
+          <t>570567</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>984242</t>
+          <t>1047645</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>274125; 478461</t>
+          <t>435206; 519577</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>516941; 709865</t>
+          <t>537411; 603879</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>808557; 1142099</t>
+          <t>992323; 1098725</t>
         </is>
       </c>
     </row>
